--- a/file/temp/DAPC.xlsx
+++ b/file/temp/DAPC.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29019"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OneDriveTeacher\OneDrive - ESCUELA COLOMBIANA DE INGENIERIA JULIO GARAVITO\UECIJG.ClassSourcecode\DAPC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R.DAPC\file\temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02751CB0-55CE-4EF8-8A44-2443CC742EB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C467EE34-3CBF-419B-9BAA-7EA90DC5FE28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{57EBF3CA-F4B8-4FD2-936E-633642D9EA06}"/>
+    <workbookView xWindow="4068" yWindow="-13068" windowWidth="23256" windowHeight="12456" xr2:uid="{57EBF3CA-F4B8-4FD2-936E-633642D9EA06}"/>
   </bookViews>
   <sheets>
     <sheet name="Actividades" sheetId="1" r:id="rId1"/>
@@ -951,23 +951,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C1ABE4D-668B-4D0E-B65B-7A27B2E0EDBD}">
   <dimension ref="B1:K27"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.59765625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="49.73046875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.5546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="49.77734375" style="1" customWidth="1"/>
     <col min="3" max="3" width="10.6640625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="9.86328125" style="3" customWidth="1"/>
-    <col min="5" max="5" width="30.265625" style="1" customWidth="1"/>
-    <col min="6" max="7" width="46.3984375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="9.265625" style="3" customWidth="1"/>
-    <col min="9" max="9" width="9.06640625" style="3"/>
-    <col min="10" max="10" width="2.59765625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="68.53125" style="1" customWidth="1"/>
-    <col min="12" max="12" width="2.59765625" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.06640625" style="1"/>
+    <col min="4" max="4" width="9.88671875" style="3" customWidth="1"/>
+    <col min="5" max="5" width="30.21875" style="1" customWidth="1"/>
+    <col min="6" max="7" width="46.44140625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="9.21875" style="3" customWidth="1"/>
+    <col min="9" max="9" width="9.109375" style="3"/>
+    <col min="10" max="10" width="2.5546875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="68.5546875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="2.5546875" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" ht="24" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:11" ht="24.6" x14ac:dyDescent="0.3">
       <c r="B1" s="20" t="s">
         <v>39</v>
       </c>
@@ -988,7 +988,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>48</v>
       </c>
@@ -1014,7 +1014,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B3" s="15" t="s">
         <v>0</v>
       </c>
@@ -1043,7 +1043,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="2:11" ht="82.5" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:11" ht="84" x14ac:dyDescent="0.3">
       <c r="B4" s="22" t="s">
         <v>47</v>
       </c>
@@ -1072,7 +1072,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="2:11" ht="82.5" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:11" ht="84" x14ac:dyDescent="0.3">
       <c r="B5" s="23"/>
       <c r="C5" s="7"/>
       <c r="D5" s="7"/>
@@ -1093,7 +1093,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="6" spans="2:11" ht="181.5" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:11" ht="184.8" x14ac:dyDescent="0.3">
       <c r="B6" s="23"/>
       <c r="C6" s="7"/>
       <c r="D6" s="7"/>
@@ -1111,7 +1111,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="7" spans="2:11" ht="66" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:11" ht="67.2" x14ac:dyDescent="0.3">
       <c r="B7" s="23"/>
       <c r="C7" s="7"/>
       <c r="D7" s="7"/>
@@ -1129,7 +1129,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="8" spans="2:11" ht="66" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:11" ht="67.2" x14ac:dyDescent="0.3">
       <c r="B8" s="23"/>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
@@ -1147,7 +1147,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="9" spans="2:11" ht="132" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:11" ht="134.4" x14ac:dyDescent="0.3">
       <c r="B9" s="23"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -1167,7 +1167,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B10" s="24"/>
       <c r="C10" s="12"/>
       <c r="D10" s="12"/>
@@ -1177,7 +1177,7 @@
       <c r="H10" s="12"/>
       <c r="I10" s="14"/>
     </row>
-    <row r="11" spans="2:11" ht="49.5" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:11" ht="50.4" x14ac:dyDescent="0.3">
       <c r="B11" s="22" t="s">
         <v>49</v>
       </c>
@@ -1203,7 +1203,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="12" spans="2:11" ht="99" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:11" ht="100.8" x14ac:dyDescent="0.3">
       <c r="B12" s="23"/>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
@@ -1223,7 +1223,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="2:11" ht="66" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:11" ht="67.2" x14ac:dyDescent="0.3">
       <c r="B13" s="23"/>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
@@ -1243,7 +1243,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B14" s="24"/>
       <c r="C14" s="12"/>
       <c r="D14" s="12"/>
@@ -1253,7 +1253,7 @@
       <c r="H14" s="12"/>
       <c r="I14" s="14"/>
     </row>
-    <row r="15" spans="2:11" ht="49.5" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:11" ht="50.4" x14ac:dyDescent="0.3">
       <c r="B15" s="22" t="s">
         <v>50</v>
       </c>
@@ -1282,7 +1282,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="16" spans="2:11" ht="49.5" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:11" ht="50.4" x14ac:dyDescent="0.3">
       <c r="B16" s="23"/>
       <c r="C16" s="7"/>
       <c r="D16" s="7"/>
@@ -1300,7 +1300,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="17" spans="2:9" ht="99" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:9" ht="100.8" x14ac:dyDescent="0.3">
       <c r="B17" s="23"/>
       <c r="C17" s="7"/>
       <c r="D17" s="7"/>
@@ -1320,7 +1320,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="2:9" ht="82.5" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:9" ht="84" x14ac:dyDescent="0.3">
       <c r="B18" s="23"/>
       <c r="C18" s="7"/>
       <c r="D18" s="7"/>
@@ -1340,7 +1340,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B19" s="24"/>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
@@ -1350,7 +1350,7 @@
       <c r="H19" s="12"/>
       <c r="I19" s="14"/>
     </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B20" s="2"/>
       <c r="C20" s="4"/>
       <c r="D20" s="4"/>
@@ -1360,7 +1360,7 @@
       <c r="H20" s="4"/>
       <c r="I20" s="4"/>
     </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B21" s="2"/>
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
@@ -1370,7 +1370,7 @@
       <c r="H21" s="4"/>
       <c r="I21" s="4"/>
     </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B22" s="2"/>
       <c r="C22" s="4"/>
       <c r="D22" s="4"/>
@@ -1380,7 +1380,7 @@
       <c r="H22" s="4"/>
       <c r="I22" s="4"/>
     </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B23" s="2"/>
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
@@ -1390,7 +1390,7 @@
       <c r="H23" s="4"/>
       <c r="I23" s="4"/>
     </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B24" s="2"/>
       <c r="C24" s="4"/>
       <c r="D24" s="4"/>
@@ -1400,7 +1400,7 @@
       <c r="H24" s="4"/>
       <c r="I24" s="4"/>
     </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B25" s="2"/>
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
@@ -1410,7 +1410,7 @@
       <c r="H25" s="4"/>
       <c r="I25" s="4"/>
     </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B26" s="2"/>
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
@@ -1420,7 +1420,7 @@
       <c r="H26" s="4"/>
       <c r="I26" s="4"/>
     </row>
-    <row r="27" spans="2:9" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B27" s="2"/>
       <c r="C27" s="4"/>
       <c r="D27" s="4"/>

--- a/file/temp/DAPC.xlsx
+++ b/file/temp/DAPC.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29113"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R.DAPC\file\temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C467EE34-3CBF-419B-9BAA-7EA90DC5FE28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3288EB3A-A169-4EA4-9F62-5A42F5E72BD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4068" yWindow="-13068" windowWidth="23256" windowHeight="12456" xr2:uid="{57EBF3CA-F4B8-4FD2-936E-633642D9EA06}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{57EBF3CA-F4B8-4FD2-936E-633642D9EA06}"/>
   </bookViews>
   <sheets>
     <sheet name="Actividades" sheetId="1" r:id="rId1"/>

--- a/file/temp/DAPC.xlsx
+++ b/file/temp/DAPC.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29113"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29115"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R.DAPC\file\temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3288EB3A-A169-4EA4-9F62-5A42F5E72BD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D90F6B29-6990-456B-B856-3889A470323D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{57EBF3CA-F4B8-4FD2-936E-633642D9EA06}"/>
   </bookViews>

--- a/file/temp/DAPC.xlsx
+++ b/file/temp/DAPC.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29115"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29121"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R.DAPC\file\temp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.DAPC\file\temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D90F6B29-6990-456B-B856-3889A470323D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76FB8765-8E08-4DBA-A4B4-CA65224C69B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{57EBF3CA-F4B8-4FD2-936E-633642D9EA06}"/>
+    <workbookView xWindow="-28898" yWindow="6562" windowWidth="28996" windowHeight="15675" xr2:uid="{57EBF3CA-F4B8-4FD2-936E-633642D9EA06}"/>
   </bookViews>
   <sheets>
     <sheet name="Actividades" sheetId="1" r:id="rId1"/>
@@ -951,23 +951,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C1ABE4D-668B-4D0E-B65B-7A27B2E0EDBD}">
   <dimension ref="B1:K27"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="2.5546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="49.77734375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.53125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="49.796875" style="1" customWidth="1"/>
     <col min="3" max="3" width="10.6640625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="9.88671875" style="3" customWidth="1"/>
-    <col min="5" max="5" width="30.21875" style="1" customWidth="1"/>
-    <col min="6" max="7" width="46.44140625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="9.21875" style="3" customWidth="1"/>
-    <col min="9" max="9" width="9.109375" style="3"/>
-    <col min="10" max="10" width="2.5546875" style="1" customWidth="1"/>
-    <col min="11" max="11" width="68.5546875" style="1" customWidth="1"/>
-    <col min="12" max="12" width="2.5546875" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.109375" style="1"/>
+    <col min="4" max="4" width="9.86328125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="30.19921875" style="1" customWidth="1"/>
+    <col min="6" max="7" width="46.46484375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="9.19921875" style="3" customWidth="1"/>
+    <col min="9" max="9" width="9.1328125" style="3"/>
+    <col min="10" max="10" width="2.53125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="68.53125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="2.53125" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.1328125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" ht="24.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:11" ht="24" x14ac:dyDescent="0.45">
       <c r="B1" s="20" t="s">
         <v>39</v>
       </c>
@@ -988,7 +988,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B2" s="1" t="s">
         <v>48</v>
       </c>
@@ -1014,7 +1014,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B3" s="15" t="s">
         <v>0</v>
       </c>
@@ -1043,7 +1043,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="4" spans="2:11" ht="84" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:11" ht="82.5" x14ac:dyDescent="0.45">
       <c r="B4" s="22" t="s">
         <v>47</v>
       </c>
@@ -1072,7 +1072,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="2:11" ht="84" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:11" ht="82.5" x14ac:dyDescent="0.45">
       <c r="B5" s="23"/>
       <c r="C5" s="7"/>
       <c r="D5" s="7"/>
@@ -1093,7 +1093,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="6" spans="2:11" ht="184.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:11" ht="181.5" x14ac:dyDescent="0.45">
       <c r="B6" s="23"/>
       <c r="C6" s="7"/>
       <c r="D6" s="7"/>
@@ -1111,7 +1111,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="7" spans="2:11" ht="67.2" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:11" ht="66" x14ac:dyDescent="0.45">
       <c r="B7" s="23"/>
       <c r="C7" s="7"/>
       <c r="D7" s="7"/>
@@ -1129,7 +1129,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="8" spans="2:11" ht="67.2" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:11" ht="66" x14ac:dyDescent="0.45">
       <c r="B8" s="23"/>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
@@ -1147,7 +1147,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="9" spans="2:11" ht="134.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:11" ht="132" x14ac:dyDescent="0.45">
       <c r="B9" s="23"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -1167,7 +1167,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B10" s="24"/>
       <c r="C10" s="12"/>
       <c r="D10" s="12"/>
@@ -1177,7 +1177,7 @@
       <c r="H10" s="12"/>
       <c r="I10" s="14"/>
     </row>
-    <row r="11" spans="2:11" ht="50.4" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:11" ht="49.5" x14ac:dyDescent="0.45">
       <c r="B11" s="22" t="s">
         <v>49</v>
       </c>
@@ -1203,7 +1203,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="12" spans="2:11" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:11" ht="99" x14ac:dyDescent="0.45">
       <c r="B12" s="23"/>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
@@ -1223,7 +1223,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="2:11" ht="67.2" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:11" ht="66" x14ac:dyDescent="0.45">
       <c r="B13" s="23"/>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
@@ -1243,7 +1243,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:11" x14ac:dyDescent="0.45">
       <c r="B14" s="24"/>
       <c r="C14" s="12"/>
       <c r="D14" s="12"/>
@@ -1253,7 +1253,7 @@
       <c r="H14" s="12"/>
       <c r="I14" s="14"/>
     </row>
-    <row r="15" spans="2:11" ht="50.4" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:11" ht="49.5" x14ac:dyDescent="0.45">
       <c r="B15" s="22" t="s">
         <v>50</v>
       </c>
@@ -1282,7 +1282,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="16" spans="2:11" ht="50.4" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:11" ht="49.5" x14ac:dyDescent="0.45">
       <c r="B16" s="23"/>
       <c r="C16" s="7"/>
       <c r="D16" s="7"/>
@@ -1300,7 +1300,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="17" spans="2:9" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:9" ht="99" x14ac:dyDescent="0.45">
       <c r="B17" s="23"/>
       <c r="C17" s="7"/>
       <c r="D17" s="7"/>
@@ -1320,7 +1320,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="2:9" ht="84" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:9" ht="82.5" x14ac:dyDescent="0.45">
       <c r="B18" s="23"/>
       <c r="C18" s="7"/>
       <c r="D18" s="7"/>
@@ -1340,7 +1340,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B19" s="24"/>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
@@ -1350,7 +1350,7 @@
       <c r="H19" s="12"/>
       <c r="I19" s="14"/>
     </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B20" s="2"/>
       <c r="C20" s="4"/>
       <c r="D20" s="4"/>
@@ -1360,7 +1360,7 @@
       <c r="H20" s="4"/>
       <c r="I20" s="4"/>
     </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B21" s="2"/>
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
@@ -1370,7 +1370,7 @@
       <c r="H21" s="4"/>
       <c r="I21" s="4"/>
     </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B22" s="2"/>
       <c r="C22" s="4"/>
       <c r="D22" s="4"/>
@@ -1380,7 +1380,7 @@
       <c r="H22" s="4"/>
       <c r="I22" s="4"/>
     </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B23" s="2"/>
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
@@ -1390,7 +1390,7 @@
       <c r="H23" s="4"/>
       <c r="I23" s="4"/>
     </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B24" s="2"/>
       <c r="C24" s="4"/>
       <c r="D24" s="4"/>
@@ -1400,7 +1400,7 @@
       <c r="H24" s="4"/>
       <c r="I24" s="4"/>
     </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B25" s="2"/>
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
@@ -1410,7 +1410,7 @@
       <c r="H25" s="4"/>
       <c r="I25" s="4"/>
     </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B26" s="2"/>
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
@@ -1420,7 +1420,7 @@
       <c r="H26" s="4"/>
       <c r="I26" s="4"/>
     </row>
-    <row r="27" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:9" x14ac:dyDescent="0.45">
       <c r="B27" s="2"/>
       <c r="C27" s="4"/>
       <c r="D27" s="4"/>

--- a/file/temp/DAPC.xlsx
+++ b/file/temp/DAPC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.DAPC\file\temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76FB8765-8E08-4DBA-A4B4-CA65224C69B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CAB57FC-828B-4930-8719-B97AB315AA06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28898" yWindow="6562" windowWidth="28996" windowHeight="15675" xr2:uid="{57EBF3CA-F4B8-4FD2-936E-633642D9EA06}"/>
   </bookViews>
